--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/81.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/81.xlsx
@@ -426,13 +426,13 @@
         <v>-3.387741040740574</v>
       </c>
       <c r="E2">
-        <v>-7.663030598811491</v>
+        <v>-9.383224278174277</v>
       </c>
       <c r="F2">
-        <v>-2.017859236994755</v>
+        <v>-1.980711929183614</v>
       </c>
       <c r="G2">
-        <v>-12.14127500903703</v>
+        <v>-11.26521485941535</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.356792529241496</v>
       </c>
       <c r="E3">
-        <v>-8.993009308150011</v>
+        <v>-10.10229052089847</v>
       </c>
       <c r="F3">
-        <v>-1.345967951481868</v>
+        <v>-1.862993465939179</v>
       </c>
       <c r="G3">
-        <v>-11.76011543634056</v>
+        <v>-11.53618534589929</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.287546277303123</v>
       </c>
       <c r="E4">
-        <v>-9.719430888130471</v>
+        <v>-10.42069231390512</v>
       </c>
       <c r="F4">
-        <v>-1.43721179253283</v>
+        <v>-1.669691447393706</v>
       </c>
       <c r="G4">
-        <v>-10.98248688466533</v>
+        <v>-10.68514396169425</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.177710622372455</v>
       </c>
       <c r="E5">
-        <v>-11.28580623286691</v>
+        <v>-11.28501296950386</v>
       </c>
       <c r="F5">
-        <v>-1.075450493851841</v>
+        <v>-1.597871993570989</v>
       </c>
       <c r="G5">
-        <v>-11.3296245392227</v>
+        <v>-10.54253073303239</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.029569926153058</v>
       </c>
       <c r="E6">
-        <v>-12.324619909067</v>
+        <v>-12.10509777128186</v>
       </c>
       <c r="F6">
-        <v>-0.9358896389303892</v>
+        <v>-1.55922202729117</v>
       </c>
       <c r="G6">
-        <v>-10.79367391971913</v>
+        <v>-10.38450105756001</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.837504177540927</v>
       </c>
       <c r="E7">
-        <v>-12.87330065719009</v>
+        <v>-12.93545761787748</v>
       </c>
       <c r="F7">
-        <v>-0.8865139715191218</v>
+        <v>-1.553220505457887</v>
       </c>
       <c r="G7">
-        <v>-10.51095116645829</v>
+        <v>-10.07147408645782</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.589929923213681</v>
       </c>
       <c r="E8">
-        <v>-12.35900019241393</v>
+        <v>-13.37118763081054</v>
       </c>
       <c r="F8">
-        <v>-1.23577934792888</v>
+        <v>-0.9244697659153952</v>
       </c>
       <c r="G8">
-        <v>-10.96985740770582</v>
+        <v>-9.712202996413245</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.276941757882788</v>
       </c>
       <c r="E9">
-        <v>-14.19458254201442</v>
+        <v>-14.58994749408147</v>
       </c>
       <c r="F9">
-        <v>-0.9723875066977354</v>
+        <v>-1.064137480231809</v>
       </c>
       <c r="G9">
-        <v>-9.429224390182476</v>
+        <v>-9.178401019708154</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.890852057884259</v>
       </c>
       <c r="E10">
-        <v>-14.05439920016748</v>
+        <v>-15.34402946148529</v>
       </c>
       <c r="F10">
-        <v>-0.5603915236087761</v>
+        <v>-1.036575211638461</v>
       </c>
       <c r="G10">
-        <v>-9.184673333588304</v>
+        <v>-8.852311188044331</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.43917503151226</v>
       </c>
       <c r="E11">
-        <v>-15.04497748004101</v>
+        <v>-16.01854835953937</v>
       </c>
       <c r="F11">
-        <v>-0.7708506878010325</v>
+        <v>-0.7836738151963688</v>
       </c>
       <c r="G11">
-        <v>-8.893027055315038</v>
+        <v>-8.256616289317718</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.9466650669518853</v>
       </c>
       <c r="E12">
-        <v>-16.12425589417891</v>
+        <v>-16.74900686092757</v>
       </c>
       <c r="F12">
-        <v>-0.1830842538794489</v>
+        <v>-0.6234965523540424</v>
       </c>
       <c r="G12">
-        <v>-7.602220103832217</v>
+        <v>-7.881397465938324</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-0.4448466624527354</v>
       </c>
       <c r="E13">
-        <v>-17.16120477849415</v>
+        <v>-17.77641581882968</v>
       </c>
       <c r="F13">
-        <v>-0.4550588097709994</v>
+        <v>-0.3163056130672766</v>
       </c>
       <c r="G13">
-        <v>-8.206493909285228</v>
+        <v>-7.072267670026721</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>0.02761823372094209</v>
       </c>
       <c r="E14">
-        <v>-17.03427018077342</v>
+        <v>-18.69114815348919</v>
       </c>
       <c r="F14">
-        <v>0.3371047956891539</v>
+        <v>-0.01903437342903479</v>
       </c>
       <c r="G14">
-        <v>-7.747851353241402</v>
+        <v>-6.652060495853265</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>0.4408093496746121</v>
       </c>
       <c r="E15">
-        <v>-18.82632272247838</v>
+        <v>-19.90104091058162</v>
       </c>
       <c r="F15">
-        <v>0.1999271537855557</v>
+        <v>-0.04706218450275607</v>
       </c>
       <c r="G15">
-        <v>-7.146514635453393</v>
+        <v>-6.668975510059088</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.7822185098093881</v>
       </c>
       <c r="E16">
-        <v>-18.18559019855179</v>
+        <v>-19.81363242503927</v>
       </c>
       <c r="F16">
-        <v>0.7488680075379265</v>
+        <v>0.5495329891978646</v>
       </c>
       <c r="G16">
-        <v>-6.718007904224787</v>
+        <v>-5.783520596026288</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>1.050823703031963</v>
       </c>
       <c r="E17">
-        <v>-19.93076129082209</v>
+        <v>-21.75743915534215</v>
       </c>
       <c r="F17">
-        <v>0.9020894692989455</v>
+        <v>0.4585351732655334</v>
       </c>
       <c r="G17">
-        <v>-5.78068793814493</v>
+        <v>-5.622899756547225</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>1.261512129059571</v>
       </c>
       <c r="E18">
-        <v>-21.06797284973002</v>
+        <v>-22.22403998805266</v>
       </c>
       <c r="F18">
-        <v>0.8163236218826958</v>
+        <v>0.931231434529432</v>
       </c>
       <c r="G18">
-        <v>-5.83645344261111</v>
+        <v>-5.352698134345365</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.436422902825349</v>
       </c>
       <c r="E19">
-        <v>-23.06889038896061</v>
+        <v>-23.62877234802677</v>
       </c>
       <c r="F19">
-        <v>1.873838985849017</v>
+        <v>1.34848506552396</v>
       </c>
       <c r="G19">
-        <v>-5.015635343165093</v>
+        <v>-4.812430648660381</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.595463899903081</v>
       </c>
       <c r="E20">
-        <v>-23.12421947022998</v>
+        <v>-23.83113756982904</v>
       </c>
       <c r="F20">
-        <v>1.254751980427585</v>
+        <v>1.688571302743297</v>
       </c>
       <c r="G20">
-        <v>-5.724520379011719</v>
+        <v>-4.51035705649021</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.762129207364841</v>
       </c>
       <c r="E21">
-        <v>-24.63672766408338</v>
+        <v>-24.93459182708876</v>
       </c>
       <c r="F21">
-        <v>1.505833453685726</v>
+        <v>1.872177280839002</v>
       </c>
       <c r="G21">
-        <v>-5.220928633342695</v>
+        <v>-4.259642031916419</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.954208962028265</v>
       </c>
       <c r="E22">
-        <v>-24.21512272286607</v>
+        <v>-25.39257889951158</v>
       </c>
       <c r="F22">
-        <v>2.399822465400203</v>
+        <v>1.930568899062339</v>
       </c>
       <c r="G22">
-        <v>-4.999433062232644</v>
+        <v>-4.029256875473627</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.182432067617362</v>
       </c>
       <c r="E23">
-        <v>-25.52894128693968</v>
+        <v>-25.70039831006257</v>
       </c>
       <c r="F23">
-        <v>1.933400258845108</v>
+        <v>1.670512893362268</v>
       </c>
       <c r="G23">
-        <v>-4.681820318256166</v>
+        <v>-3.798589758614995</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.457905173657753</v>
       </c>
       <c r="E24">
-        <v>-25.69966319165808</v>
+        <v>-25.6900485074411</v>
       </c>
       <c r="F24">
-        <v>2.168123132632764</v>
+        <v>2.035236433875668</v>
       </c>
       <c r="G24">
-        <v>-4.573620619422067</v>
+        <v>-3.280534487911203</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.780873546959935</v>
       </c>
       <c r="E25">
-        <v>-24.62966305161985</v>
+        <v>-26.08608627974278</v>
       </c>
       <c r="F25">
-        <v>1.990413473710186</v>
+        <v>1.813871812825556</v>
       </c>
       <c r="G25">
-        <v>-3.624954357349233</v>
+        <v>-3.617686044407573</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.147272768763468</v>
       </c>
       <c r="E26">
-        <v>-25.64148916063121</v>
+        <v>-26.13160132265157</v>
       </c>
       <c r="F26">
-        <v>2.151925236438423</v>
+        <v>2.187656035990777</v>
       </c>
       <c r="G26">
-        <v>-4.220146687742057</v>
+        <v>-3.676007467828453</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.551918854505466</v>
       </c>
       <c r="E27">
-        <v>-25.08362981548024</v>
+        <v>-26.2296960209327</v>
       </c>
       <c r="F27">
-        <v>1.917901504738729</v>
+        <v>1.895101520344075</v>
       </c>
       <c r="G27">
-        <v>-4.165477696004145</v>
+        <v>-3.361543281828857</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>3.981893202047332</v>
       </c>
       <c r="E28">
-        <v>-24.81649110985594</v>
+        <v>-25.76283353590872</v>
       </c>
       <c r="F28">
-        <v>1.949550109730087</v>
+        <v>1.874639188760122</v>
       </c>
       <c r="G28">
-        <v>-4.420181938313157</v>
+        <v>-3.569079201610226</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>4.425135863167534</v>
       </c>
       <c r="E29">
-        <v>-25.8740191562857</v>
+        <v>-25.74090873332495</v>
       </c>
       <c r="F29">
-        <v>2.376495639337369</v>
+        <v>1.622333388480643</v>
       </c>
       <c r="G29">
-        <v>-4.978614984863107</v>
+        <v>-3.383379549588929</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>4.86849212725391</v>
       </c>
       <c r="E30">
-        <v>-24.98403996112217</v>
+        <v>-25.09763029085623</v>
       </c>
       <c r="F30">
-        <v>1.907389522397203</v>
+        <v>1.65106117000973</v>
       </c>
       <c r="G30">
-        <v>-4.704468527584074</v>
+        <v>-3.335550708679734</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>5.294642114751428</v>
       </c>
       <c r="E31">
-        <v>-25.19027182266786</v>
+        <v>-25.11766538228721</v>
       </c>
       <c r="F31">
-        <v>1.521214579620907</v>
+        <v>1.691926190724635</v>
       </c>
       <c r="G31">
-        <v>-3.472351114509479</v>
+        <v>-3.205360708154688</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>5.691094370473618</v>
       </c>
       <c r="E32">
-        <v>-24.85749576526597</v>
+        <v>-24.98897397617607</v>
       </c>
       <c r="F32">
-        <v>1.965651915305703</v>
+        <v>1.564942438079888</v>
       </c>
       <c r="G32">
-        <v>-3.914757449941172</v>
+        <v>-3.308821905555916</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>6.044541371621423</v>
       </c>
       <c r="E33">
-        <v>-23.99435877489481</v>
+        <v>-24.65214023130983</v>
       </c>
       <c r="F33">
-        <v>2.119034080342866</v>
+        <v>1.650643672838719</v>
       </c>
       <c r="G33">
-        <v>-4.061470852983374</v>
+        <v>-3.519691746180136</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>6.343042099029521</v>
       </c>
       <c r="E34">
-        <v>-22.48978736788314</v>
+        <v>-24.43893512794975</v>
       </c>
       <c r="F34">
-        <v>1.665756407735393</v>
+        <v>1.78715365061566</v>
       </c>
       <c r="G34">
-        <v>-3.933176253031476</v>
+        <v>-3.64830485697215</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>6.58406445696093</v>
       </c>
       <c r="E35">
-        <v>-23.51287283279611</v>
+        <v>-23.88686120617427</v>
       </c>
       <c r="F35">
-        <v>1.985774616254509</v>
+        <v>1.526075439540535</v>
       </c>
       <c r="G35">
-        <v>-4.542093267739783</v>
+        <v>-3.930847468856203</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>6.764825875048798</v>
       </c>
       <c r="E36">
-        <v>-23.20009033471194</v>
+        <v>-23.72070783391318</v>
       </c>
       <c r="F36">
-        <v>1.736175920647379</v>
+        <v>1.524123805939539</v>
       </c>
       <c r="G36">
-        <v>-5.156511121301566</v>
+        <v>-3.819514876512768</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>6.88414199925692</v>
       </c>
       <c r="E37">
-        <v>-21.22953692347717</v>
+        <v>-22.72512493439323</v>
       </c>
       <c r="F37">
-        <v>1.756068335458206</v>
+        <v>1.388738751095599</v>
       </c>
       <c r="G37">
-        <v>-5.174217191118497</v>
+        <v>-3.910525432958977</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>6.941888414935793</v>
       </c>
       <c r="E38">
-        <v>-21.88453157509323</v>
+        <v>-22.36455558680559</v>
       </c>
       <c r="F38">
-        <v>1.671364455052346</v>
+        <v>1.664765680321645</v>
       </c>
       <c r="G38">
-        <v>-5.109447228557567</v>
+        <v>-3.834001898248856</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>6.934278393725114</v>
       </c>
       <c r="E39">
-        <v>-21.85818775565984</v>
+        <v>-21.72323330687086</v>
       </c>
       <c r="F39">
-        <v>1.708246685294591</v>
+        <v>1.46514570359502</v>
       </c>
       <c r="G39">
-        <v>-4.380402022978364</v>
+        <v>-3.664149465895616</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>6.860726400073372</v>
       </c>
       <c r="E40">
-        <v>-20.55778821737675</v>
+        <v>-21.18942520850198</v>
       </c>
       <c r="F40">
-        <v>1.544473479556712</v>
+        <v>1.662951555709514</v>
       </c>
       <c r="G40">
-        <v>-4.647807537723142</v>
+        <v>-4.284592917973689</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>6.732552382225538</v>
       </c>
       <c r="E41">
-        <v>-20.88273131822001</v>
+        <v>-20.40771192615408</v>
       </c>
       <c r="F41">
-        <v>1.628541173797222</v>
+        <v>1.648248034309822</v>
       </c>
       <c r="G41">
-        <v>-5.05380703983176</v>
+        <v>-4.476474813186742</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>6.568896376585215</v>
       </c>
       <c r="E42">
-        <v>-19.86803949339453</v>
+        <v>-20.27730939697711</v>
       </c>
       <c r="F42">
-        <v>2.195169328334168</v>
+        <v>1.394676488638866</v>
       </c>
       <c r="G42">
-        <v>-5.036986012431218</v>
+        <v>-4.117586197224763</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>6.385904323334562</v>
       </c>
       <c r="E43">
-        <v>-19.21243431971372</v>
+        <v>-18.86279622433303</v>
       </c>
       <c r="F43">
-        <v>2.091802330343234</v>
+        <v>1.585409739868258</v>
       </c>
       <c r="G43">
-        <v>-5.199121083773126</v>
+        <v>-4.5839226175786</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>6.194822715184939</v>
       </c>
       <c r="E44">
-        <v>-18.50283739881014</v>
+        <v>-19.0488351724174</v>
       </c>
       <c r="F44">
-        <v>2.095592939578445</v>
+        <v>1.446094910065437</v>
       </c>
       <c r="G44">
-        <v>-5.632896297586599</v>
+        <v>-4.16319068374233</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>5.998248156068816</v>
       </c>
       <c r="E45">
-        <v>-17.38240896686584</v>
+        <v>-18.47046726974443</v>
       </c>
       <c r="F45">
-        <v>1.89895839897151</v>
+        <v>1.615237593308262</v>
       </c>
       <c r="G45">
-        <v>-5.134578255991623</v>
+        <v>-4.337886047312084</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>5.793864478661978</v>
       </c>
       <c r="E46">
-        <v>-17.95228355237954</v>
+        <v>-17.36673059411461</v>
       </c>
       <c r="F46">
-        <v>1.787920718830653</v>
+        <v>1.567917933790743</v>
       </c>
       <c r="G46">
-        <v>-4.841331591284006</v>
+        <v>-4.55653068532864</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>5.579397511060778</v>
       </c>
       <c r="E47">
-        <v>-17.72086661736009</v>
+        <v>-16.94949483121102</v>
       </c>
       <c r="F47">
-        <v>2.022408336275915</v>
+        <v>1.761639934609436</v>
       </c>
       <c r="G47">
-        <v>-4.908140545370594</v>
+        <v>-4.654094210698543</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>5.349145156480454</v>
       </c>
       <c r="E48">
-        <v>-14.77961634886375</v>
+        <v>-16.22137043458737</v>
       </c>
       <c r="F48">
-        <v>1.412927079257345</v>
+        <v>1.24492091609116</v>
       </c>
       <c r="G48">
-        <v>-6.328986074192178</v>
+        <v>-5.009351280934284</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>5.098802899304964</v>
       </c>
       <c r="E49">
-        <v>-16.35565621635305</v>
+        <v>-15.1464611987632</v>
       </c>
       <c r="F49">
-        <v>1.957487526183712</v>
+        <v>1.624321470247362</v>
       </c>
       <c r="G49">
-        <v>-5.548370830704714</v>
+        <v>-4.677423824364731</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>4.826674813788062</v>
       </c>
       <c r="E50">
-        <v>-14.38450474268751</v>
+        <v>-15.01938954506875</v>
       </c>
       <c r="F50">
-        <v>1.821477882318061</v>
+        <v>1.285997998861182</v>
       </c>
       <c r="G50">
-        <v>-5.64066065200057</v>
+        <v>-5.07833759600986</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>4.525912736849384</v>
       </c>
       <c r="E51">
-        <v>-14.63784648029072</v>
+        <v>-14.0783050845532</v>
       </c>
       <c r="F51">
-        <v>1.767378863976031</v>
+        <v>1.487046080990233</v>
       </c>
       <c r="G51">
-        <v>-5.689656495741993</v>
+        <v>-4.803366143440036</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>4.193891750646523</v>
       </c>
       <c r="E52">
-        <v>-13.16025433404515</v>
+        <v>-13.88408015694759</v>
       </c>
       <c r="F52">
-        <v>1.384176103440979</v>
+        <v>1.561986823186699</v>
       </c>
       <c r="G52">
-        <v>-5.471813356314908</v>
+        <v>-4.950666964015239</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>3.830709721930825</v>
       </c>
       <c r="E53">
-        <v>-13.35075798430371</v>
+        <v>-13.27113676999542</v>
       </c>
       <c r="F53">
-        <v>1.369823809820075</v>
+        <v>1.433207170012682</v>
       </c>
       <c r="G53">
-        <v>-5.765882405568727</v>
+        <v>-5.181898001705552</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>3.433445680358449</v>
       </c>
       <c r="E54">
-        <v>-14.21519492981955</v>
+        <v>-12.85038739031102</v>
       </c>
       <c r="F54">
-        <v>1.526429980788933</v>
+        <v>1.561486489275408</v>
       </c>
       <c r="G54">
-        <v>-5.730647796567062</v>
+        <v>-5.630423922458814</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>3.007619369338177</v>
       </c>
       <c r="E55">
-        <v>-12.95213691455799</v>
+        <v>-12.66774576909036</v>
       </c>
       <c r="F55">
-        <v>1.19819271089924</v>
+        <v>1.492286333180343</v>
       </c>
       <c r="G55">
-        <v>-6.406029147075931</v>
+        <v>-5.815181095682719</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>2.556412422849784</v>
       </c>
       <c r="E56">
-        <v>-13.53121916957883</v>
+        <v>-11.52280923711825</v>
       </c>
       <c r="F56">
-        <v>1.476867102344633</v>
+        <v>1.194120456747078</v>
       </c>
       <c r="G56">
-        <v>-6.262594839240167</v>
+        <v>-5.605496533102865</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>2.081744917530891</v>
       </c>
       <c r="E57">
-        <v>-12.17922844021872</v>
+        <v>-12.22843984120662</v>
       </c>
       <c r="F57">
-        <v>1.522087678863458</v>
+        <v>1.339328292253414</v>
       </c>
       <c r="G57">
-        <v>-6.437666150031042</v>
+        <v>-6.233260513014418</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.592176014451664</v>
       </c>
       <c r="E58">
-        <v>-11.35934299258432</v>
+        <v>-11.48647694444865</v>
       </c>
       <c r="F58">
-        <v>0.9001345222283387</v>
+        <v>1.603951915812522</v>
       </c>
       <c r="G58">
-        <v>-7.661681117267117</v>
+        <v>-6.268925894873617</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.092002759254133</v>
       </c>
       <c r="E59">
-        <v>-10.3872672691629</v>
+        <v>-10.69512821182714</v>
       </c>
       <c r="F59">
-        <v>1.511033944240501</v>
+        <v>1.440314562328702</v>
       </c>
       <c r="G59">
-        <v>-7.273328943222129</v>
+        <v>-6.306055904448431</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.5870408357763561</v>
       </c>
       <c r="E60">
-        <v>-10.79477205793243</v>
+        <v>-10.57308609704705</v>
       </c>
       <c r="F60">
-        <v>1.157895950222655</v>
+        <v>1.296130588932225</v>
       </c>
       <c r="G60">
-        <v>-6.98598778277961</v>
+        <v>-5.999183763719793</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.08726260485526682</v>
       </c>
       <c r="E61">
-        <v>-11.44373209349351</v>
+        <v>-10.36638907583299</v>
       </c>
       <c r="F61">
-        <v>1.400425358414294</v>
+        <v>1.196762948762008</v>
       </c>
       <c r="G61">
-        <v>-7.735856287217532</v>
+        <v>-6.731035519734442</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.4033377695677055</v>
       </c>
       <c r="E62">
-        <v>-10.65610879143038</v>
+        <v>-9.591491213269128</v>
       </c>
       <c r="F62">
-        <v>0.8495013930996217</v>
+        <v>1.433409291658965</v>
       </c>
       <c r="G62">
-        <v>-6.47619029721751</v>
+        <v>-6.743556650793421</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.8756824122010944</v>
       </c>
       <c r="E63">
-        <v>-9.128939761600323</v>
+        <v>-9.042557119255214</v>
       </c>
       <c r="F63">
-        <v>1.391800397016346</v>
+        <v>1.203386574514793</v>
       </c>
       <c r="G63">
-        <v>-8.544798109518576</v>
+        <v>-7.200081892973855</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.319965150735984</v>
       </c>
       <c r="E64">
-        <v>-9.336471578290681</v>
+        <v>-9.801523263177032</v>
       </c>
       <c r="F64">
-        <v>1.410089092535354</v>
+        <v>1.227954294947021</v>
       </c>
       <c r="G64">
-        <v>-7.859258351805684</v>
+        <v>-7.116574616482505</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.732366810995682</v>
       </c>
       <c r="E65">
-        <v>-10.190583640453</v>
+        <v>-9.080658679949192</v>
       </c>
       <c r="F65">
-        <v>1.335965120598048</v>
+        <v>1.412781286594452</v>
       </c>
       <c r="G65">
-        <v>-7.609376154756458</v>
+        <v>-7.355786700387851</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.103922698743111</v>
       </c>
       <c r="E66">
-        <v>-10.30980572474352</v>
+        <v>-8.728354222897961</v>
       </c>
       <c r="F66">
-        <v>1.223940026513054</v>
+        <v>1.131484283951796</v>
       </c>
       <c r="G66">
-        <v>-8.314133603404533</v>
+        <v>-7.27893421185925</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.429566118548043</v>
       </c>
       <c r="E67">
-        <v>-8.769512547127013</v>
+        <v>-8.789049253199005</v>
       </c>
       <c r="F67">
-        <v>0.7812174113520528</v>
+        <v>1.100307848380033</v>
       </c>
       <c r="G67">
-        <v>-8.125490336856757</v>
+        <v>-7.438826653597391</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.707899194583815</v>
       </c>
       <c r="E68">
-        <v>-10.43056034401291</v>
+        <v>-8.546431107236497</v>
       </c>
       <c r="F68">
-        <v>0.9758555865182414</v>
+        <v>0.9623846758139158</v>
       </c>
       <c r="G68">
-        <v>-8.221415619995737</v>
+        <v>-7.741492884789746</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.936484734359943</v>
       </c>
       <c r="E69">
-        <v>-8.69921944545429</v>
+        <v>-8.379600761529458</v>
       </c>
       <c r="F69">
-        <v>0.5853706481451797</v>
+        <v>1.030511267754953</v>
       </c>
       <c r="G69">
-        <v>-7.735373299468177</v>
+        <v>-7.465678161716991</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.118503727643352</v>
       </c>
       <c r="E70">
-        <v>-7.110429219197755</v>
+        <v>-8.240144231664367</v>
       </c>
       <c r="F70">
-        <v>1.174836063609905</v>
+        <v>0.90315309304414</v>
       </c>
       <c r="G70">
-        <v>-7.431955173833582</v>
+        <v>-7.492211158996476</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.258023739354527</v>
       </c>
       <c r="E71">
-        <v>-9.517472681038035</v>
+        <v>-8.412311453923808</v>
       </c>
       <c r="F71">
-        <v>1.148184170792234</v>
+        <v>0.8433747877885165</v>
       </c>
       <c r="G71">
-        <v>-8.353025865578349</v>
+        <v>-7.269256181659992</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.35921441675114</v>
       </c>
       <c r="E72">
-        <v>-8.440063211996312</v>
+        <v>-7.912497390248642</v>
       </c>
       <c r="F72">
-        <v>0.8523062451255008</v>
+        <v>0.9884500845104052</v>
       </c>
       <c r="G72">
-        <v>-8.03742861642621</v>
+        <v>-6.853254917022819</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.428808794849703</v>
       </c>
       <c r="E73">
-        <v>-10.6203828676142</v>
+        <v>-8.301798653781447</v>
       </c>
       <c r="F73">
-        <v>1.313057448441031</v>
+        <v>0.9454561595703052</v>
       </c>
       <c r="G73">
-        <v>-8.343537114361947</v>
+        <v>-7.153114597779727</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.47056050192398</v>
       </c>
       <c r="E74">
-        <v>-10.27264278980896</v>
+        <v>-8.212180659814296</v>
       </c>
       <c r="F74">
-        <v>0.4507244970245369</v>
+        <v>0.8503794625465891</v>
       </c>
       <c r="G74">
-        <v>-6.980708857216379</v>
+        <v>-7.241373429426902</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.485707321999892</v>
       </c>
       <c r="E75">
-        <v>-9.049858464764263</v>
+        <v>-8.999342955420374</v>
       </c>
       <c r="F75">
-        <v>0.949687460263805</v>
+        <v>0.4325128396739897</v>
       </c>
       <c r="G75">
-        <v>-7.56407451461146</v>
+        <v>-7.026091430443701</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.471968364932473</v>
       </c>
       <c r="E76">
-        <v>-9.743237095444389</v>
+        <v>-9.36255789862193</v>
       </c>
       <c r="F76">
-        <v>1.113142572919009</v>
+        <v>0.662581117025316</v>
       </c>
       <c r="G76">
-        <v>-7.174057990889637</v>
+        <v>-7.010103230567723</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.424521263050217</v>
       </c>
       <c r="E77">
-        <v>-10.78230411753529</v>
+        <v>-10.20330077352962</v>
       </c>
       <c r="F77">
-        <v>0.7166213212817474</v>
+        <v>0.8469003194548312</v>
       </c>
       <c r="G77">
-        <v>-7.354786785209455</v>
+        <v>-6.49012123035569</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.337124487992826</v>
       </c>
       <c r="E78">
-        <v>-10.89468586277383</v>
+        <v>-9.914889319499553</v>
       </c>
       <c r="F78">
-        <v>0.6502036512926858</v>
+        <v>0.7753873615711498</v>
       </c>
       <c r="G78">
-        <v>-6.83806038350254</v>
+        <v>-6.516273058924872</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.203030721223489</v>
       </c>
       <c r="E79">
-        <v>-11.13702159036625</v>
+        <v>-9.836526528222688</v>
       </c>
       <c r="F79">
-        <v>0.9527176282232457</v>
+        <v>0.9468676976246755</v>
       </c>
       <c r="G79">
-        <v>-7.158038462078567</v>
+        <v>-6.214810380989021</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.016926009837277</v>
       </c>
       <c r="E80">
-        <v>-12.28249803981058</v>
+        <v>-10.69955968831073</v>
       </c>
       <c r="F80">
-        <v>0.9901846858518673</v>
+        <v>0.7031810601713254</v>
       </c>
       <c r="G80">
-        <v>-6.771549054299338</v>
+        <v>-6.188253887008217</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.770477065244622</v>
       </c>
       <c r="E81">
-        <v>-11.99274925173392</v>
+        <v>-11.44800990115808</v>
       </c>
       <c r="F81">
-        <v>0.5522160712155323</v>
+        <v>1.052653528431784</v>
       </c>
       <c r="G81">
-        <v>-6.303215414333299</v>
+        <v>-5.545245769429152</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.458772965401127</v>
       </c>
       <c r="E82">
-        <v>-13.31195453089584</v>
+        <v>-11.47496839586755</v>
       </c>
       <c r="F82">
-        <v>1.08533427920703</v>
+        <v>0.7573786542342886</v>
       </c>
       <c r="G82">
-        <v>-5.473327588177754</v>
+        <v>-5.442181405205773</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.082285243404681</v>
       </c>
       <c r="E83">
-        <v>-13.10067651759048</v>
+        <v>-13.1511961801457</v>
       </c>
       <c r="F83">
-        <v>1.241952047319527</v>
+        <v>0.7387387309364941</v>
       </c>
       <c r="G83">
-        <v>-6.048469400110829</v>
+        <v>-5.354303742268899</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.640169915491633</v>
       </c>
       <c r="E84">
-        <v>-14.34786095916854</v>
+        <v>-13.63850077131048</v>
       </c>
       <c r="F84">
-        <v>1.249891120507957</v>
+        <v>0.8983932939476541</v>
       </c>
       <c r="G84">
-        <v>-5.854752151450223</v>
+        <v>-5.336326155014493</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.141431051391343</v>
       </c>
       <c r="E85">
-        <v>-15.49550123171312</v>
+        <v>-14.80589787012726</v>
       </c>
       <c r="F85">
-        <v>0.8108000680408287</v>
+        <v>0.8531197019150499</v>
       </c>
       <c r="G85">
-        <v>-6.497253784578612</v>
+        <v>-4.997469782300127</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.5979307315931762</v>
       </c>
       <c r="E86">
-        <v>-17.04977827186033</v>
+        <v>-15.92193635770121</v>
       </c>
       <c r="F86">
-        <v>0.341462836595282</v>
+        <v>0.7921352937209503</v>
       </c>
       <c r="G86">
-        <v>-5.464244807745271</v>
+        <v>-4.594488300938836</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.02187349319507805</v>
       </c>
       <c r="E87">
-        <v>-18.15326160159932</v>
+        <v>-17.37632451227497</v>
       </c>
       <c r="F87">
-        <v>1.0488413816441</v>
+        <v>0.9696196367099668</v>
       </c>
       <c r="G87">
-        <v>-5.922017985840257</v>
+        <v>-4.513625708718283</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.5660461166132738</v>
       </c>
       <c r="E88">
-        <v>-18.78069554286382</v>
+        <v>-18.96124394557676</v>
       </c>
       <c r="F88">
-        <v>0.5657673335579294</v>
+        <v>0.9229427902970202</v>
       </c>
       <c r="G88">
-        <v>-5.218545023531009</v>
+        <v>-4.163830316167153</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.147187759573701</v>
       </c>
       <c r="E89">
-        <v>-21.026635937414</v>
+        <v>-19.71459079457609</v>
       </c>
       <c r="F89">
-        <v>0.3517437044314267</v>
+        <v>0.790533231163936</v>
       </c>
       <c r="G89">
-        <v>-5.135682600953664</v>
+        <v>-4.302244162154206</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.702202144815986</v>
       </c>
       <c r="E90">
-        <v>-22.40181819881195</v>
+        <v>-21.92147438982758</v>
       </c>
       <c r="F90">
-        <v>0.6525263934901356</v>
+        <v>0.9810792713602952</v>
       </c>
       <c r="G90">
-        <v>-5.375576089197291</v>
+        <v>-3.661556996516641</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.209900677417531</v>
       </c>
       <c r="E91">
-        <v>-23.99278886101402</v>
+        <v>-23.69170180602057</v>
       </c>
       <c r="F91">
-        <v>1.120500132190674</v>
+        <v>0.8586747337182233</v>
       </c>
       <c r="G91">
-        <v>-5.132468774362004</v>
+        <v>-4.107205876730497</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.655239003933723</v>
       </c>
       <c r="E92">
-        <v>-26.04163445893314</v>
+        <v>-25.47641147010325</v>
       </c>
       <c r="F92">
-        <v>0.5992416603050574</v>
+        <v>0.9741392092596408</v>
       </c>
       <c r="G92">
-        <v>-5.062258020073194</v>
+        <v>-3.854425753185135</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>3.021474102150937</v>
       </c>
       <c r="E93">
-        <v>-27.75113777234581</v>
+        <v>-28.09107188946604</v>
       </c>
       <c r="F93">
-        <v>1.164928789472423</v>
+        <v>0.8576160801774456</v>
       </c>
       <c r="G93">
-        <v>-4.994420432617707</v>
+        <v>-3.700981850587043</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>3.293321761714494</v>
       </c>
       <c r="E94">
-        <v>-32.40637266927433</v>
+        <v>-29.74889471775822</v>
       </c>
       <c r="F94">
-        <v>0.9628187403329829</v>
+        <v>0.5641586440616927</v>
       </c>
       <c r="G94">
-        <v>-5.35336648496069</v>
+        <v>-3.697992548030218</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>3.463507339121514</v>
       </c>
       <c r="E95">
-        <v>-33.06005905932307</v>
+        <v>-32.00748994721515</v>
       </c>
       <c r="F95">
-        <v>0.5671440801813822</v>
+        <v>0.6664454509593757</v>
       </c>
       <c r="G95">
-        <v>-5.036795428076066</v>
+        <v>-3.675655017308653</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>3.52056116667823</v>
       </c>
       <c r="E96">
-        <v>-34.84410420959377</v>
+        <v>-34.23788279517083</v>
       </c>
       <c r="F96">
-        <v>0.7611013373424697</v>
+        <v>0.5631778570567781</v>
       </c>
       <c r="G96">
-        <v>-4.985708377917161</v>
+        <v>-4.035120607825267</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>3.46889919374922</v>
       </c>
       <c r="E97">
-        <v>-37.15158273634393</v>
+        <v>-36.78440978274981</v>
       </c>
       <c r="F97">
-        <v>0.960413161395253</v>
+        <v>0.3475099186357185</v>
       </c>
       <c r="G97">
-        <v>-5.381839265471371</v>
+        <v>-3.675816883473301</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>3.302383302324958</v>
       </c>
       <c r="E98">
-        <v>-39.07195912495779</v>
+        <v>-38.88823143897569</v>
       </c>
       <c r="F98">
-        <v>0.234036838330631</v>
+        <v>0.3256120263427135</v>
       </c>
       <c r="G98">
-        <v>-4.764152759681514</v>
+        <v>-3.892135348059175</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>3.048233397166576</v>
       </c>
       <c r="E99">
-        <v>-41.73975157679912</v>
+        <v>-41.22183989477601</v>
       </c>
       <c r="F99">
-        <v>0.06717133707810136</v>
+        <v>0.4546145103480833</v>
       </c>
       <c r="G99">
-        <v>-4.472885039373961</v>
+        <v>-3.272028682033356</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>2.698189897344124</v>
       </c>
       <c r="E100">
-        <v>-45.31732781200643</v>
+        <v>-44.18184606561529</v>
       </c>
       <c r="F100">
-        <v>0.1913204164704689</v>
+        <v>0.3597970923214435</v>
       </c>
       <c r="G100">
-        <v>-5.090443618678854</v>
+        <v>-3.794597930135183</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>2.319908859316438</v>
       </c>
       <c r="E101">
-        <v>-47.76574971827597</v>
+        <v>-46.00322754739337</v>
       </c>
       <c r="F101">
-        <v>0.1372984362968991</v>
+        <v>-0.1737121050841753</v>
       </c>
       <c r="G101">
-        <v>-4.292884642795064</v>
+        <v>-4.283814916085537</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>1.87094433802438</v>
       </c>
       <c r="E102">
-        <v>-49.05679830126121</v>
+        <v>-48.57523448645017</v>
       </c>
       <c r="F102">
-        <v>0.3265257155880014</v>
+        <v>-0.1926792335060755</v>
       </c>
       <c r="G102">
-        <v>-5.474523309200484</v>
+        <v>-3.83762300099673</v>
       </c>
     </row>
   </sheetData>
